--- a/Horarios/HorarioWAN_202.xlsx
+++ b/Horarios/HorarioWAN_202.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{636BD453-A386-4481-BA20-18F700D07395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{636BD453-A386-4481-BA20-18F700D07395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D910CC60-549C-4512-93CC-ABE6B1B321DE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="WAN_201" sheetId="5" r:id="rId1"/>
@@ -644,66 +644,66 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -722,6 +722,18 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -732,18 +744,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -790,10 +790,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1135,7 +1131,7 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -1156,7 +1152,7 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -1167,7 +1163,7 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
@@ -1240,19 +1236,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -1261,25 +1257,25 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="47" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1287,34 +1283,34 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -1344,19 +1340,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -1365,24 +1361,24 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1390,34 +1386,34 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="42"/>
+      <c r="D24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -1447,19 +1443,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -1468,27 +1464,27 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1496,30 +1492,30 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="35"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="36"/>
       <c r="F35" s="39"/>
       <c r="G35" s="6"/>
@@ -1551,19 +1547,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -1572,72 +1568,83 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="18"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="18"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="18"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="19"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="C12:C13"/>
@@ -1654,27 +1661,16 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1691,8 +1687,7 @@
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="14.6328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.36328125" customWidth="1"/>
@@ -1725,7 +1720,7 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -1745,7 +1740,7 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -1755,11 +1750,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1779,7 +1774,7 @@
       <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
@@ -1789,7 +1784,7 @@
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
-      <c r="G7" s="15"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
@@ -1828,19 +1823,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1848,25 +1843,25 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="47" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1874,34 +1869,34 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -1931,19 +1926,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1951,58 +1946,58 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
+      <c r="C23" s="30"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="15"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -2032,19 +2027,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2052,27 +2047,27 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2080,30 +2075,30 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="35"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="36"/>
       <c r="F35" s="39"/>
       <c r="G35" s="6"/>
@@ -2135,19 +2130,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2155,68 +2150,84 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="18"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="18"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="18"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="19"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="C30:C31"/>
@@ -2229,33 +2240,17 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="G30:G31"/>
     <mergeCell ref="G32:G34"/>
-    <mergeCell ref="C21:C26"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E42:E44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="97" orientation="portrait" r:id="rId1"/>
@@ -2318,7 +2313,7 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -2350,7 +2345,7 @@
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -2371,11 +2366,11 @@
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
@@ -2411,7 +2406,7 @@
       <c r="F6" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" s="3" t="s">
@@ -2421,7 +2416,7 @@
       <c r="D7" s="49"/>
       <c r="E7" s="49"/>
       <c r="F7" s="49"/>
-      <c r="G7" s="15"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" s="3" t="s">
@@ -2460,19 +2455,19 @@
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -2491,11 +2486,11 @@
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2510,15 +2505,15 @@
       <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="47" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -2536,13 +2531,13 @@
       <c r="B15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -2557,13 +2552,13 @@
       <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -2571,10 +2566,10 @@
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
@@ -2604,19 +2599,19 @@
       <c r="B21" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -2635,11 +2630,11 @@
       <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="31"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -2656,15 +2651,15 @@
       <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="20" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="29" t="s">
+      <c r="E23" s="30"/>
+      <c r="F23" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2684,15 +2679,15 @@
       <c r="B24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="15" t="s">
+      <c r="D24" s="25"/>
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="33"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="14"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -2708,21 +2703,21 @@
       <c r="B25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="14"/>
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="30"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="29"/>
       <c r="G26" s="6"/>
       <c r="P26" s="1"/>
     </row>
@@ -2758,19 +2753,19 @@
       <c r="B30" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -2790,11 +2785,11 @@
       <c r="B31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -2811,15 +2806,15 @@
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2839,15 +2834,15 @@
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="14"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -2863,19 +2858,19 @@
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="35"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="14"/>
       <c r="P34" s="1"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="36"/>
       <c r="F35" s="39"/>
       <c r="G35" s="6"/>
@@ -2913,19 +2908,19 @@
       <c r="B39" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="15" t="s">
+      <c r="E39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="G39" s="18" t="s">
         <v>57</v>
       </c>
       <c r="I39" s="1"/>
@@ -2944,11 +2939,11 @@
       <c r="B40" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="24"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="19"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -2965,13 +2960,13 @@
       <c r="B41" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="24"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="19"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -2994,27 +2989,27 @@
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="23" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="23" t="s">
+      <c r="F42" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="24"/>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="21"/>
+      <c r="C43" s="25"/>
       <c r="D43" s="54"/>
       <c r="E43" s="54"/>
       <c r="F43" s="54"/>
-      <c r="G43" s="25"/>
+      <c r="G43" s="20"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>120</v>
@@ -3036,7 +3031,7 @@
       <c r="B44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="22"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="55"/>
       <c r="E44" s="55"/>
       <c r="F44" s="55"/>
@@ -3103,11 +3098,34 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="G23:G25"/>
     <mergeCell ref="G39:G43"/>
@@ -3124,34 +3142,11 @@
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="F42:F44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3210,7 +3205,7 @@
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="48" t="s">
@@ -3242,7 +3237,7 @@
       <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="49"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -3263,7 +3258,7 @@
       <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="49"/>
       <c r="E5" s="49"/>
       <c r="F5" s="49"/>
@@ -3352,19 +3347,19 @@
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="1"/>
@@ -3383,11 +3378,11 @@
       <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
       <c r="J13" s="1" t="s">
         <v>14</v>
       </c>
@@ -3402,15 +3397,15 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="47" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
@@ -3428,13 +3423,13 @@
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -3449,13 +3444,13 @@
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
@@ -3463,10 +3458,10 @@
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
       <c r="G17" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
@@ -3496,19 +3491,19 @@
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>13</v>
       </c>
       <c r="I21" s="1"/>
@@ -3527,11 +3522,11 @@
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="14"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
       <c r="I22" s="1"/>
       <c r="J22" t="s">
         <v>12</v>
@@ -3548,13 +3543,13 @@
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -3574,15 +3569,15 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="42"/>
+      <c r="D24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
       <c r="J24" t="s">
         <v>31</v>
       </c>
@@ -3598,21 +3593,21 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="15"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
       <c r="O25" s="1"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="6"/>
       <c r="O26" s="1"/>
     </row>
@@ -3648,19 +3643,19 @@
       <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="1"/>
@@ -3680,11 +3675,11 @@
       <c r="B31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
       <c r="J31" t="s">
         <v>12</v>
       </c>
@@ -3701,17 +3696,17 @@
       <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -3731,13 +3726,13 @@
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="29" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="14"/>
       <c r="J33" t="s">
         <v>31</v>
       </c>
@@ -3753,19 +3748,19 @@
       <c r="B34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="35"/>
       <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
+      <c r="G34" s="14"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
       <c r="E35" s="36"/>
       <c r="F35" s="39"/>
       <c r="G35" s="6"/>
@@ -3803,19 +3798,19 @@
       <c r="B39" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="21" t="s">
         <v>16</v>
       </c>
       <c r="I39" s="1"/>
@@ -3835,11 +3830,11 @@
       <c r="B40" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="18"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
         <v>12</v>
@@ -3856,13 +3851,13 @@
       <c r="B41" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="18"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
         <v>15</v>
@@ -3885,25 +3880,25 @@
       <c r="B42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="29" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="18"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="19"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
       <c r="K43" s="1">
         <f>SUM(K3:K41)</f>
         <v>111</v>
@@ -3922,10 +3917,901 @@
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K46">
+        <f>5*4*5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K47">
+        <f>4*5</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="K48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K49">
+        <f>120-5-4</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K50" s="1">
+        <f>K3+K12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K51" s="1">
+        <f>K13+K21+K30+K39</f>
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K52" s="1">
+        <f>K4+K14+K22+K31+K40</f>
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="1">
+        <f>K5+K15+K23+K24+K32+K33+K41</f>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="K54">
+        <f>SUM(K50:K53)</f>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:O54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="2"/>
+    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="13" max="14" width="10.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B2" s="4"/>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <f>K3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="1">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+      <c r="M12" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="33"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="14"/>
+      <c r="J13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="46"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="47"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="1">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
+      <c r="I22" s="1"/>
+      <c r="J22" t="s">
+        <v>12</v>
+      </c>
+      <c r="K22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="42"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M23" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="42"/>
+      <c r="D24" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="25"/>
+      <c r="G24" s="14"/>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="42"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="14"/>
+      <c r="O25" s="1"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="43"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="6"/>
+      <c r="O26" s="1"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="1"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="4"/>
+      <c r="C29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="1"/>
+    </row>
+    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="1">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="O30" s="1"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="31"/>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="O31" s="1"/>
+    </row>
+    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="10">
+        <v>2</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="14"/>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>5</v>
+      </c>
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="14"/>
+      <c r="O34" s="1"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="6"/>
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="1">
+        <f>3+2.5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="22"/>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="22"/>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
+      <c r="M41" s="10">
+        <f>4.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="N41" s="2">
+        <f>2+2.5+5</f>
+        <v>9.5</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="19"/>
+      <c r="G42" s="22"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="23"/>
+      <c r="K43" s="1">
+        <f>SUM(K3:K41)</f>
+        <v>111</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="9">
+        <f>SUM(M3:M41)</f>
+        <v>59.5</v>
+      </c>
+      <c r="N43" s="9">
+        <f>SUM(N3:N41)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="6"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.35">
@@ -4046,895 +4932,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B72F34B-8139-4D0E-8882-03145DDD5E1F}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:O54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" style="2"/>
-    <col min="3" max="4" width="12.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="4"/>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1">
-        <f>2.5+2.5+2.5+2.5+2</f>
-        <v>12</v>
-      </c>
-      <c r="M3" s="9">
-        <f>K3</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <f>2.5+2.5+2.5</f>
-        <v>7.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="M5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="15"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="15"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="1">
-        <f>3+2.5+3+2</f>
-        <v>10.5</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="15"/>
-      <c r="J13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="M13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <f>2+2.5+2+2</f>
-        <v>8.5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="43"/>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="43"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B19" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B20" s="4"/>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1">
-        <f>2.5+3</f>
-        <v>5.5</v>
-      </c>
-      <c r="M21" s="2">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="14"/>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>12</v>
-      </c>
-      <c r="K22">
-        <f>2.5+2</f>
-        <v>4.5</v>
-      </c>
-      <c r="N22" s="2">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="15"/>
-      <c r="J24" t="s">
-        <v>31</v>
-      </c>
-      <c r="K24">
-        <v>4.5</v>
-      </c>
-      <c r="N24" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="15"/>
-      <c r="O25" s="1"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="6"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O27" s="1"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B28" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B29" s="4"/>
-      <c r="C29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O29" s="1"/>
-    </row>
-    <row r="30" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="1">
-        <f>3+2.5+2+3</f>
-        <v>10.5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="O30" s="1"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="14"/>
-      <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31">
-        <f>2+2.5+2</f>
-        <v>6.5</v>
-      </c>
-      <c r="N31" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="O31" s="1"/>
-    </row>
-    <row r="32" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K32" s="1">
-        <v>2</v>
-      </c>
-      <c r="M32" s="10">
-        <v>2</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="15"/>
-      <c r="J33" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="1">
-        <v>5</v>
-      </c>
-      <c r="N33" s="2">
-        <v>5</v>
-      </c>
-      <c r="O33" s="1"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="15"/>
-      <c r="O34" s="1"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="6"/>
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O37" s="1"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="4"/>
-      <c r="C38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K39" s="1">
-        <f>3+2.5</f>
-        <v>5.5</v>
-      </c>
-      <c r="M39" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B40" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="18"/>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="27"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="18"/>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-      <c r="M41" s="10">
-        <f>4.5</f>
-        <v>4.5</v>
-      </c>
-      <c r="N41" s="2">
-        <f>2+2.5+5</f>
-        <v>9.5</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="24"/>
-      <c r="G42" s="18"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="19"/>
-      <c r="K43" s="1">
-        <f>SUM(K3:K41)</f>
-        <v>111</v>
-      </c>
-      <c r="L43" s="1"/>
-      <c r="M43" s="9">
-        <f>SUM(M3:M41)</f>
-        <v>59.5</v>
-      </c>
-      <c r="N43" s="9">
-        <f>SUM(N3:N41)</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K46">
-        <f>5*4*5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K47">
-        <f>4*5</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="K48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K49">
-        <f>120-5-4</f>
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K50" s="1">
-        <f>K3+K12</f>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J51" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K51" s="1">
-        <f>K13+K21+K30+K39</f>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="52" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K52" s="1">
-        <f>K4+K14+K22+K31+K40</f>
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="53" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="J53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K53" s="1">
-        <f>K5+K15+K23+K24+K32+K33+K41</f>
-        <v>34.5</v>
-      </c>
-    </row>
-    <row r="54" spans="10:11" x14ac:dyDescent="0.35">
-      <c r="K54">
-        <f>SUM(K50:K53)</f>
-        <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>